--- a/daybook-generated-files/8.xlsx
+++ b/daybook-generated-files/8.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\file\HV\Capital DayBook\11. NOV\XLSX File\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\10.37.221.58\Shared Files\HV\Capital DayBook\2026\01. JAN\XLSX File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DDA41BDA-6191-4E01-B7DC-1E4EC8CCB336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DC87B4D-9C36-4058-AEF6-15066EA206DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{F2FF7986-6289-4DF9-B1FD-79444C25CB72}"/>
+    <workbookView xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" xr2:uid="{60119F98-3790-4501-B3F5-75200700A250}"/>
   </bookViews>
   <sheets>
     <sheet name="Suspense Head Report" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="32">
   <si>
     <t>WESTERN RAILWAY</t>
   </si>
   <si>
-    <t>SUSPENSE HEAD   REPORT FROM 1/11/2025 TO 30/11/2025</t>
-  </si>
-  <si>
-    <t>ALLOCATION : 43417803-***</t>
+    <t>SUSPENSE HEAD   REPORT FROM 1/1/2026 TO 31/1/2026</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 43656403-***</t>
   </si>
   <si>
     <t>SECTION</t>
@@ -67,37 +67,55 @@
     <t>UNIQUE_WORK_ID</t>
   </si>
   <si>
-    <t>01-JV</t>
-  </si>
-  <si>
-    <t>081832501941</t>
-  </si>
-  <si>
-    <t>24/11/2025</t>
-  </si>
-  <si>
-    <t>RITES INSPECTION BILL-----------------------------</t>
-  </si>
-  <si>
-    <t>***</t>
-  </si>
-  <si>
-    <t>7728</t>
+    <t>X-I</t>
+  </si>
+  <si>
+    <t>08180125008369</t>
+  </si>
+  <si>
+    <t>08180125701435</t>
+  </si>
+  <si>
+    <t>21/01/2026</t>
+  </si>
+  <si>
+    <t>ALPINE ASSOCIATE-KHARGHAR DIST RAIGAD</t>
+  </si>
+  <si>
+    <t>SITC of electrical work at Bhatia boarding</t>
+  </si>
+  <si>
+    <t>812226.27</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>SECURITY</t>
+    <t>ELECTRICAL</t>
+  </si>
+  <si>
+    <t>0818WC22000071 - WR/RJT/Elect./2022/0010</t>
   </si>
   <si>
     <t>RKTS01812G</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>150465183002</t>
   </si>
   <si>
     <t>Allocation Total</t>
+  </si>
+  <si>
+    <t>812226</t>
+  </si>
+  <si>
+    <t>ALLOCATION : 43656466-***</t>
+  </si>
+  <si>
+    <t>146200.73</t>
+  </si>
+  <si>
+    <t>146201</t>
   </si>
 </sst>
 </file>
@@ -495,19 +513,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EEBA8AE-4F8C-4E6C-9FFB-75A302E139EA}">
-  <dimension ref="A1:L7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40363072-0EDD-4955-914B-AE0863EC14BC}">
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.42578125" customWidth="1"/>
-    <col min="2" max="3" width="13.42578125" customWidth="1"/>
+    <col min="2" max="3" width="15.5703125" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="47" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" customWidth="1"/>
-    <col min="7" max="7" width="6" customWidth="1"/>
+    <col min="5" max="5" width="37.140625" customWidth="1"/>
+    <col min="6" max="6" width="34.140625" customWidth="1"/>
+    <col min="7" max="7" width="9.7109375" customWidth="1"/>
     <col min="8" max="8" width="7.28515625" customWidth="1"/>
-    <col min="9" max="9" width="8.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" customWidth="1"/>
+    <col min="10" max="10" width="39.42578125" customWidth="1"/>
     <col min="11" max="11" width="12.42578125" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" customWidth="1"/>
   </cols>
@@ -602,50 +620,150 @@
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="G12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="J12" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="F7" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>21</v>
+      <c r="L12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
   </mergeCells>
